--- a/Data/Counts-transcript.xlsx
+++ b/Data/Counts-transcript.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nnseh/Desktop/Github/NCLTEE/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6950A081-CE1C-7248-9996-1A890D987465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F5037B73-C99F-3C4B-BA29-B8C454A2A71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="3000" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{D7831DFC-5F48-D34B-92FE-B1E3530E0E8B}"/>
+    <workbookView xWindow="1780" yWindow="3040" windowWidth="28040" windowHeight="13260" activeTab="2" xr2:uid="{D7831DFC-5F48-D34B-92FE-B1E3530E0E8B}"/>
   </bookViews>
   <sheets>
     <sheet name="NH4+" sheetId="1" r:id="rId1"/>
     <sheet name="F2" sheetId="2" r:id="rId2"/>
+    <sheet name="CFU" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Abundance_Tetraselmis" localSheetId="0">'NH4+'!$A$1:$J$505</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +43,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{2718ACC0-4EF1-794F-A387-198D10BF46FC}" name="Abundance_Tetraselmis" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/nnseh/Desktop/Github/NCLTEE/Data/Abundance_Tetraselmis.csv" thousands="_x0000_" tab="0" semicolon="1">
+    <textPr sourceFile="/Users/nnseh/Desktop/Github/NCLTEE/Data/Abundance_Tetraselmis.csv" thousands="_x0000_" tab="0" semicolon="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +140,27 @@
   <si>
     <t>p4</t>
   </si>
+  <si>
+    <t>CFU</t>
+  </si>
+  <si>
+    <t>count_of</t>
+  </si>
+  <si>
+    <t>Cells_mL</t>
+  </si>
+  <si>
+    <t>caldilution</t>
+  </si>
+  <si>
+    <t>Cells per mL in Culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mL added </t>
+  </si>
+  <si>
+    <t>log cells</t>
+  </si>
 </sst>
 </file>
 
@@ -172,9 +195,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7B96F-068A-4D4D-93CB-38A6C5DB8602}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" bestFit="1" customWidth="1"/>
@@ -600,11 +624,11 @@
         <v>17</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I16" si="0">(H3*10000)/(1*4)</f>
+        <f t="shared" ref="I3:I28" si="0">(H3*10000)/(1*4)</f>
         <v>42500</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J16" si="1">LOG10(I3)</f>
+        <f t="shared" ref="J3:J28" si="1">LOG10(I3)</f>
         <v>4.6283889300503116</v>
       </c>
     </row>
@@ -1050,7 +1074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1064,10 +1088,27 @@
         <v>2</v>
       </c>
       <c r="E17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>62</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+        <v>155000</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>5.1903316981702918</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1081,10 +1122,27 @@
         <v>2</v>
       </c>
       <c r="E18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>70</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="0"/>
+        <v>175000</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>5.2430380486862944</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1098,10 +1156,27 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>63</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="0"/>
+        <v>157500</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>5.1972805581256196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -1115,10 +1190,27 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>61</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+        <v>152500</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>5.1832698436828046</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>5</v>
       </c>
@@ -1132,10 +1224,27 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>43</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="0"/>
+        <v>107500</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>5.0314084642516246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>6</v>
       </c>
@@ -1149,10 +1258,27 @@
         <v>2</v>
       </c>
       <c r="E22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>48</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="0"/>
+        <v>120000</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>5.0791812460476251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>7</v>
       </c>
@@ -1166,10 +1292,27 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>83</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="0"/>
+        <v>207500</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>5.3170181010481112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>8</v>
       </c>
@@ -1183,10 +1326,27 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24">
+        <v>88</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+        <v>220000</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>5.3424226808222066</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>9</v>
       </c>
@@ -1200,10 +1360,27 @@
         <v>2</v>
       </c>
       <c r="E25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>74</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+        <v>185000</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>5.2671717284030137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>10</v>
       </c>
@@ -1217,10 +1394,27 @@
         <v>2</v>
       </c>
       <c r="E26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>42</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
+        <v>105000</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>5.0211892990699383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>11</v>
       </c>
@@ -1234,10 +1428,27 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>77</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+        <v>192500</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>5.2844307338445198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>12</v>
       </c>
@@ -1251,7 +1462,264 @@
         <v>2</v>
       </c>
       <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>44</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="0"/>
+        <v>110000</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>5.0413926851582254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29">
         <v>3</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>7</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1356,11 +1824,11 @@
         <v>17</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I16" si="0">(H3*10000)/(1*4)</f>
+        <f t="shared" ref="I3:I28" si="0">(H3*10000)/(1*4)</f>
         <v>42500</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J16" si="1">LOG10(I3)</f>
+        <f t="shared" ref="J3:J28" si="1">LOG10(I3)</f>
         <v>4.6283889300503116</v>
       </c>
     </row>
@@ -1806,7 +2274,7 @@
         <v>4.8129133566428557</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1822,9 +2290,25 @@
       <c r="E17">
         <v>3</v>
       </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F17" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>23</v>
+      </c>
+      <c r="I17" s="1">
+        <f>(H17*10000)/(F17*4)</f>
+        <v>230000</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>5.3617278360175931</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -1840,9 +2324,25 @@
       <c r="E18">
         <v>3</v>
       </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F18" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>19</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" ref="I18:I28" si="2">(H18*10000)/(F18*4)</f>
+        <v>190000</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>5.2787536009528289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -1858,9 +2358,25 @@
       <c r="E19">
         <v>3</v>
       </c>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F19" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>37</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="2"/>
+        <v>370000</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>5.568201724066995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1876,9 +2392,25 @@
       <c r="E20">
         <v>3</v>
       </c>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>27</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="2"/>
+        <v>270000</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>5.4313637641589869</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -1894,9 +2426,25 @@
       <c r="E21">
         <v>3</v>
       </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F21" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>5.3010299956639813</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -1912,9 +2460,25 @@
       <c r="E22">
         <v>3</v>
       </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F22" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="2"/>
+        <v>40000</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>4.6020599913279625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -1930,9 +2494,25 @@
       <c r="E23">
         <v>3</v>
       </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F23" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>5.4771212547196626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -1948,9 +2528,25 @@
       <c r="E24">
         <v>3</v>
       </c>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F24" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24">
+        <v>38</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="2"/>
+        <v>380000</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>5.5797835966168101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -1966,9 +2562,25 @@
       <c r="E25">
         <v>3</v>
       </c>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F25" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>47</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="2"/>
+        <v>470000</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>5.6720978579357171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -1984,9 +2596,25 @@
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F26" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>38</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="2"/>
+        <v>380000</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>5.5797835966168101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2002,9 +2630,25 @@
       <c r="E27">
         <v>3</v>
       </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F27" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>22</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="2"/>
+        <v>220000</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>5.3424226808222066</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2020,7 +2664,974 @@
       <c r="E28">
         <v>3</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="F28" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>47</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="2"/>
+        <v>470000</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>5.6720978579357171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4462F7FB-AD62-C545-8B45-3520963E76D2}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>-6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1">
+        <f>10^G2*I2</f>
+        <v>220000000</v>
+      </c>
+      <c r="K2" s="1">
+        <f>(J2*M2)/300</f>
+        <v>15667.283866666667</v>
+      </c>
+      <c r="L2">
+        <f>LOG10(K2)</f>
+        <v>4.194993712233571</v>
+      </c>
+      <c r="M2">
+        <v>2.1364477999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>-6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J25" si="0">10^G3*I3</f>
+        <v>20000000</v>
+      </c>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K9" si="1">(J3*M3)/300</f>
+        <v>1424.2985333333334</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L25" si="2">LOG10(K3)</f>
+        <v>3.1536010270753465</v>
+      </c>
+      <c r="M3">
+        <v>2.1364477999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>-6</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>48</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="0"/>
+        <v>480000000</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="1"/>
+        <v>36319.612639999999</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="2"/>
+        <v>4.5601412079876047</v>
+      </c>
+      <c r="M4">
+        <v>2.2699757899999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>-6</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
+        <v>40000000</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="1"/>
+        <v>2575.8590533333336</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>3.4109220954757156</v>
+      </c>
+      <c r="M5">
+        <v>1.93189429E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>-7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="0"/>
+        <v>2500000000</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="1"/>
+        <v>144035.76666666666</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>5.1584703486036894</v>
+      </c>
+      <c r="M6">
+        <v>1.7284292E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>-5</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>63</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="0"/>
+        <v>63000000</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="1"/>
+        <v>3167.7393299999999</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>3.5007494367431073</v>
+      </c>
+      <c r="M7">
+        <v>1.5084472999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>-6</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>59</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
+        <v>590000000</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="1"/>
+        <v>32962.367013333336</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>4.5180183906439781</v>
+      </c>
+      <c r="M8">
+        <v>1.6760525599999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>-6</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>73</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>730000000</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="1"/>
+        <v>42058.443866666668</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>4.6238532000521078</v>
+      </c>
+      <c r="M9">
+        <v>1.7284292E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>-6</v>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>22</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="0"/>
+        <v>220000000</v>
+      </c>
+      <c r="K14" s="1">
+        <f>(J14*M2)/300</f>
+        <v>15667.283866666667</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>4.194993712233571</v>
+      </c>
+      <c r="M14">
+        <v>2.1364477999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>-6</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="0"/>
+        <v>20000000</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" ref="K15:K21" si="3">(J15*M3)/300</f>
+        <v>1424.2985333333334</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>3.1536010270753465</v>
+      </c>
+      <c r="M15">
+        <v>2.1364477999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>-6</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>48</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="0"/>
+        <v>480000000</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="3"/>
+        <v>36319.612639999999</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>4.5601412079876047</v>
+      </c>
+      <c r="M16">
+        <v>2.2699757899999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>-6</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="0"/>
+        <v>40000000</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" si="3"/>
+        <v>2575.8590533333336</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>3.4109220954757156</v>
+      </c>
+      <c r="M17">
+        <v>1.93189429E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>-7</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18">
+        <v>25</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="0"/>
+        <v>2500000000</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="3"/>
+        <v>144035.76666666666</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>5.1584703486036894</v>
+      </c>
+      <c r="M18">
+        <v>1.7284292E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>-5</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>63</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="0"/>
+        <v>63000000</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" si="3"/>
+        <v>3167.7393299999999</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>3.5007494367431073</v>
+      </c>
+      <c r="M19">
+        <v>1.5084472999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>-6</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20">
+        <v>59</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="0"/>
+        <v>590000000</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" si="3"/>
+        <v>32962.367013333336</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>4.5180183906439781</v>
+      </c>
+      <c r="M20">
+        <v>1.6760525599999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>-6</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>73</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="0"/>
+        <v>730000000</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="3"/>
+        <v>42058.443866666668</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>4.6238532000521078</v>
+      </c>
+      <c r="M21">
+        <v>1.7284292E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
